--- a/education_forms/031_university_clinical_field_experience_verification_form--education_forms.xlsx
+++ b/education_forms/031_university_clinical_field_experience_verification_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>student_details</t>
+          <t>Student Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>clinical_details</t>
+          <t>Clinical Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>verification</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please verify clinical field experience below</t>
-        </is>
-      </c>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -598,17 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hours_completed</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter hours completed in each role</t>
-        </is>
-      </c>
+          <t>Hours Completed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,90 +617,82 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Select evaluation for each role</t>
-        </is>
-      </c>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>supervisor_signature</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>supervisor_signature</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>supervisor_name</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter supervisor name</t>
-        </is>
-      </c>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>university_signature</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>university_signature</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -720,22 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>university_name</t>
+          <t>hours_worked</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>university_name</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter university name</t>
-        </is>
-      </c>
+          <t>Hours Worked</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -747,39 +727,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>evaluation_scale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Select role</t>
-        </is>
-      </c>
+          <t>Evaluation Scale</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -792,93 +768,89 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>university_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>University Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hours_worked</t>
+          <t>supervisor_signature</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hours_worked</t>
+          <t>Supervisor Signature</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>evaluation_scale</t>
+          <t>supervisor_name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>evaluation_scale</t>
+          <t>Supervisor Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>university_signature</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter any comments</t>
-        </is>
-      </c>
+          <t>University Signature</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,261 +860,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_completed</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hours_completed</t>
+          <t>Role 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>supervisor_signature</t>
+          <t>university_clinical_field_experience_verification_form</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>supervisor_signature</t>
+          <t>University Clinical Field Experience Verification Form</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>supervisor_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>supervisor_name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter supervisor name</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>university_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>university_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hours_worked</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>hours_worked</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>evaluation_scale</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>evaluation_scale</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Enter any comments</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1157,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>clinical_field_experience_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clinical Field Experience 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1207,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>clinical_field_experience_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clinical Field Experience 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1224,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>clinical_field_experience_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clinical Field Experience 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1241,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1377,165 +1134,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>role_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>role_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>role_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>field_experience</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Field Experience</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>research_project</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Research Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>evaluation_scale_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>evaluation_scale_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>evaluation_scale_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
